--- a/Python/Analise/Dados_alunos.xlsx
+++ b/Python/Analise/Dados_alunos.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TI\Desktop\Doc_Arthur\Faculdade\Python\Analise\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17970" windowHeight="6030"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Página1" sheetId="1" r:id="rId5"/>
+    <sheet name="Página1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="58">
   <si>
     <t>Nome</t>
   </si>
@@ -82,9 +90,6 @@
     <t>jogo da velha</t>
   </si>
   <si>
-    <t>Infelizmente</t>
-  </si>
-  <si>
     <t>Sim</t>
   </si>
   <si>
@@ -148,24 +153,12 @@
     <t>Feminino</t>
   </si>
   <si>
-    <t>não sei</t>
-  </si>
-  <si>
-    <t>um pouco</t>
-  </si>
-  <si>
-    <t>não muito</t>
-  </si>
-  <si>
     <t>sertanejo</t>
   </si>
   <si>
     <t>Arthur Cruz Viana</t>
   </si>
   <si>
-    <t>Fut</t>
-  </si>
-  <si>
     <t>Isabella Barros</t>
   </si>
   <si>
@@ -194,20 +187,27 @@
   </si>
   <si>
     <t xml:space="preserve">sertanejo </t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>PHP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -218,32 +218,39 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -251,7 +258,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -441,21 +448,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="22.25"/>
-    <col customWidth="1" min="4" max="4" width="28.38"/>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -496,12 +506,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="1">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>14</v>
@@ -510,13 +520,13 @@
         <v>15</v>
       </c>
       <c r="E2" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>16</v>
@@ -537,12 +547,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B3" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>14</v>
@@ -551,13 +561,13 @@
         <v>21</v>
       </c>
       <c r="E3" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F3" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>22</v>
@@ -566,30 +576,30 @@
         <v>23</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B4" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="E4" s="1">
         <v>4.5</v>
@@ -598,51 +608,51 @@
         <v>2.5</v>
       </c>
       <c r="G4" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="B5" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="1">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>7</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E5" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>17</v>
@@ -660,94 +670,94 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="1">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1">
+        <v>4</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="1">
+        <v>6</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="F7" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="B8" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -756,16 +766,16 @@
         <v>21</v>
       </c>
       <c r="E8" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>17</v>
@@ -777,18 +787,18 @@
         <v>17</v>
       </c>
       <c r="L8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="B9" s="1">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>14</v>
@@ -797,39 +807,39 @@
         <v>15</v>
       </c>
       <c r="E9" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F9" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="B10" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>14</v>
@@ -838,16 +848,16 @@
         <v>21</v>
       </c>
       <c r="E10" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="F10" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>17</v>
@@ -859,33 +869,33 @@
         <v>17</v>
       </c>
       <c r="L10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="1">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B11" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>45</v>
+      <c r="E11" s="1">
+        <v>6</v>
       </c>
       <c r="F11" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>16</v>
@@ -894,24 +904,24 @@
         <v>19</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B12" s="1">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>14</v>
@@ -920,16 +930,16 @@
         <v>21</v>
       </c>
       <c r="E12" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="F12" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>17</v>
@@ -941,33 +951,33 @@
         <v>17</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B13" s="1">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E13" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F13" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>16</v>
@@ -982,36 +992,36 @@
         <v>17</v>
       </c>
       <c r="L13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="1">
+        <v>21</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="E14" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>17</v>
@@ -1023,23 +1033,25 @@
         <v>17</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B15" s="1">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="E15" s="1">
         <v>5.5</v>
       </c>
@@ -1047,33 +1059,33 @@
         <v>0.5</v>
       </c>
       <c r="G15" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B16" s="1">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>14</v>
@@ -1082,16 +1094,16 @@
         <v>21</v>
       </c>
       <c r="E16" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F16" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>17</v>
@@ -1103,13 +1115,13 @@
         <v>17</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>